--- a/حسابداری/بانک ها/رسالت ابوالفضل/1405/14050331 - 14050431.xlsx
+++ b/حسابداری/بانک ها/رسالت ابوالفضل/1405/14050331 - 14050431.xlsx
@@ -1,33 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\رسالت ابوالفضل\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB97ADF6-A83D-4DB6-AF91-32B06668B1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34F217B-EDF1-4E10-B694-19A458E69239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Table1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$P$95</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="39">
-  <si>
-    <t>صورت حساب سپرده</t>
-  </si>
-  <si>
-    <t>صورت‌حساب سپرده 10.11651202.1 مربوط به سپرده حقيقي قرض الحسنه پس انداز حقيقي ريالی ابوالفضل شريفي ميناب از تاریخ 1405/03/31 تا تاریخ 1405/04/06 برای ارز ریال .</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="282">
   <si>
     <t/>
   </si>
@@ -53,9 +49,6 @@
     <t>مانده</t>
   </si>
   <si>
-    <t>یادداشت</t>
-  </si>
-  <si>
     <t>995</t>
   </si>
   <si>
@@ -101,9 +94,6 @@
     <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 80021897 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت (2) - شماره مرجع 802614244565 شماره پيگيري 244565_سند تراکنش کارت</t>
   </si>
   <si>
-    <t>جمع کل واریزها: 0 - جمع کل برداشت‌ها: 47,471,900</t>
-  </si>
-  <si>
     <t>صورت‌حساب سپرده 10.11651202.1 مربوط به سپرده حقيقي قرض الحسنه پس انداز حقيقي ريالی ابوالفضل شريفي ميناب از تاریخ 1405/02/31 تا تاریخ 1405/03/27 برای ارز ریال .</t>
   </si>
   <si>
@@ -138,6 +128,747 @@
   </si>
   <si>
     <t>پست بند شاپینگ بگ</t>
+  </si>
+  <si>
+    <t>1405/04/08</t>
+  </si>
+  <si>
+    <t>17:51:56</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 14077990 - پذيرنده ایران مارکت - پرداخت الکترونیک سامان - شماره مرجع 862774775979 شماره پيگيري 724435_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/09</t>
+  </si>
+  <si>
+    <t>09:26:33</t>
+  </si>
+  <si>
+    <t>09:26:34</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 6037691636112419 متعلق به رضا رضایی از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1367752733 شماره پيگيري 413166_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>21:43:22</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 33478627 - پذيرنده NOT - پرداخت الکترونیک سداد (2) - شماره مرجع 323570403201 شماره پيگيري 23988_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/10</t>
+  </si>
+  <si>
+    <t>09:30:09</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 6037998238447295 متعلق به طلعت مدنی از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1370679037 شماره پيگيري 339510_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/11</t>
+  </si>
+  <si>
+    <t>10:19:33</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از اينترنت 13202508 - پذيرنده مبین نت - پرداخت الکترونیک سامان - شماره مرجع 224782309178 شماره پيگيري 365863_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/17</t>
+  </si>
+  <si>
+    <t>12:37:30</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 15341545 - پذيرنده یکبار مصرف نگین - پرداخت الکترونیک سامان - شماره مرجع 863026838700 شماره پيگيري 807156_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>12:39:06</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 15341545 - پذيرنده یکبار مصرف نگین - پرداخت الکترونیک سامان - شماره مرجع 863026887840 شماره پيگيري 866296_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>18:28:50</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 597064 - پذيرنده مسقط حاج رسول - پرداخت الکترونیک پاسارگاد - شماره مرجع 141012649486 شماره پيگيري 12235_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>19:03:29</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 8566550 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت - شماره مرجع 351210159010 شماره پيگيري 159010_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/18</t>
+  </si>
+  <si>
+    <t>10:06:07</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 6219861947396205 متعلق به نیما کربلائی زاده تبریز از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1390760097 شماره پيگيري 420817_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>10:22:23</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 5047061023282037 متعلق به حمد ناصرزاده از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1390800400 شماره پيگيري 461115_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>10:48:38</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 5859831820741014 متعلق به احمد عفیفه لاری از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1390870197 شماره پيگيري 530915_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>13:18:15</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 2816178 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت - شماره مرجع 351287924251 شماره پيگيري 924251_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>19:50:34</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 6274121193748548 به کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از اينترنت 19002 - پذيرنده مدرن - بانک اقتصاد نوین - شماره مرجع 999942355265 شماره پيگيري 355265_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/20</t>
+  </si>
+  <si>
+    <t>11:59:31</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 5748954 - پذيرنده ض بق ن امزاس - کارت اعتباری ایران کیش - شماره مرجع 489541910264 شماره پيگيري 75_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>12:01:21</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 362898 - پذيرنده خی اطی پردی س - پرداخت الکترونیک پاسارگاد - شماره مرجع 141406684705 شماره پيگيري 4217_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>12:31:16</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 14644007 - پذيرنده ابزار نادر - پرداخت الکترونیک سامان - شماره مرجع 863109608232 شماره پيگيري 756688_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>13:04:21</t>
+  </si>
+  <si>
+    <t>واریز پایا IRR,4670061682_واریز پایا بابت شماره پیگیری 14050420012264680862 از بانک ملت شعبه 1235220 توسط حسین علیمردانی بیرگانی</t>
+  </si>
+  <si>
+    <t>19:24:13</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 6037691636112419 متعلق به رضا رضایی از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1396753942 شماره پيگيري 414734_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>20:09:59</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 6037998185952255 متعلق به ه فراع ی لدج از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1396907368 شماره پيگيري 568155_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/21</t>
+  </si>
+  <si>
+    <t>07:39:07</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 6037997216519638 متعلق به کاوه زاده ابراهیم از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1397730251 شماره پيگيري 391044_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>07:46:46</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 12155557 - پذيرنده قنادی حافظ - پرداخت الکترونیک سامان - شماره مرجع 863133533207 شماره پيگيري 381663_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>17:51:13</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 41830692 - پذيرنده سوپرمارکت آرمان - سایان کارت - شماره مرجع 091986634093 شماره پيگيري 634093_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>17:56:40</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 31248899 - پذيرنده سوپر هخامنش - پرداخت الکترونیک سامان - شماره مرجع 863149910367 شماره پيگيري 593823_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>22:00:42</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 31267235 - پذيرنده پایانه شماره 53276213 - پرداخت نوین آرین - شماره مرجع 517214476732 شماره پيگيري 239031_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>22:01:06</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 31267235 - پذيرنده پایانه شماره 53276213 - پرداخت نوین آرین - شماره مرجع 517214497998 شماره پيگيري 250344_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>22:06:36</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 31267235 - پذيرنده پایانه شماره 53276213 - پرداخت نوین آرین - شماره مرجع 517214577911 شماره پيگيري 331588_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>22:23:11</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 8623310 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت - شماره مرجع 351664443549 شماره پيگيري 443549_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/22</t>
+  </si>
+  <si>
+    <t>09:19:04</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از اينترنت 80080727 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت (2) - شماره مرجع 802798868168 شماره پيگيري 868168_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>09:39:48</t>
+  </si>
+  <si>
+    <t>برداشت از سپرده بابت کارمزد اعتبارسنجي(تاييد رمز)(نامه 02.32780)_اعتبارسنجي کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 80933683 - پذيرنده سوپر مارکت - پرداخت الکترونیک پاسارگاد - شماره مرجع 142338560362 شماره پيگيري 12836</t>
+  </si>
+  <si>
+    <t>09:40:14</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 80933683 - پذيرنده سوپر مارکت - پرداخت الکترونیک پاسارگاد - شماره مرجع 142338560790 شماره پيگيري 12837_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>09:47:05</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 5029081069134191 متعلق به سمانه سلطانی ویس از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1400738504 شماره پيگيري 399348_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>10:24:30</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 5859831073281734 متعلق به محمدقاسم پتی آبادی از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1400844283 شماره پيگيري 505122_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>11:16:36</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 6219861931114291 متعلق به فتاح خسروی از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1401004203 شماره پيگيري 665042_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>11:28:25</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 99199758 - پذيرنده پرداخت الکترونیک سپهر - مبنا کارت آریا (اینفوتک) - شماره مرجع 129870790578 شماره پيگيري 790578_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>13:27:56</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 31341813 - پذيرنده پایانه شماره 31814313 - پرداخت نوین آرین - شماره مرجع 517222077727 شماره پيگيري 815578_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>13:34:35</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 30871654 - پذيرنده پایانه شماره 45617803 - پرداخت نوین آرین - شماره مرجع 517222201824 شماره پيگيري 907048_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>13:36:45</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 5909096 - پذيرنده DASTPOKHT - آسان پرداخت پرشین - شماره مرجع 072144773767 شماره پيگيري 31203_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>22:55:03</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 9111406 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت - شماره مرجع 351785825411 شماره پيگيري 825411_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/23</t>
+  </si>
+  <si>
+    <t>09:58:53</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 70532022 - پذيرنده فروشگاه خواروبار شهباز - پرداخت الکترونیک پاسارگاد - شماره مرجع 142339678386 شماره پيگيري 39334_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>10:06:57</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 9278037 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت - شماره مرجع 351812780285 شماره پيگيري 780285_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>14:38:58</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از اينترنت 80080727 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت (2) - شماره مرجع 802817274278 شماره پيگيري 274278_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>17:42:45</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 99199758 - پذيرنده پرداخت الکترونیک سپهر - مبنا کارت آریا (اینفوتک) - شماره مرجع 129874183842 شماره پيگيري 183842_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>21:41:07</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از اينترنت 80080727 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت (2) - شماره مرجع 802822884112 شماره پيگيري 884112_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>22:26:05</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 31199388 - پذيرنده میوه فروشی سحر - پرداخت الکترونیک سامان - شماره مرجع 863222631947 شماره پيگيري 400403_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>22:28:36</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 31199388 - پذيرنده میوه فروشی سحر - پرداخت الکترونیک سامان - شماره مرجع 863222698041 شماره پيگيري 461497_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>22:30:12</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 34068455 - پذيرنده Not - پرداخت الکترونیک سداد (2) - شماره مرجع 323685685150 شماره پيگيري 2791_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1405/04/24</t>
+  </si>
+  <si>
+    <t>08:28:39</t>
+  </si>
+  <si>
+    <t>کارمزد ارسال پیامک اردیبهشت 1405_برداشت بابت فایل (GW-1784103672439)</t>
+  </si>
+  <si>
+    <t>10:48:09</t>
+  </si>
+  <si>
+    <t>10:48:10</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 6104337327987408 متعلق به  شکرالله  رحمان دوست از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1406493525 شماره پيگيري 154439_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>17:01:51</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از اينترنت 10749015 - پذيرنده اسنپ - پرداخت الکترونیک سامان - شماره مرجع 224827129901 شماره پيگيري 336586_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>20:07:05</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 99199758 - پذيرنده پرداخت الکترونیک سپهر - مبنا کارت آریا (اینفوتک) - شماره مرجع 129877412241 شماره پيگيري 412241_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/25</t>
+  </si>
+  <si>
+    <t>10:03:11</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 41548268 - پذيرنده نانوایی بهاری مستعلی - سایان کارت - شماره مرجع 228428301327 شماره پيگيري 301327_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>12:00:05</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از اينترنت 22583078 - پذيرنده پرداخت الکترونیک سپهر - مبنا کارت آریا (اینفوتک) - شماره مرجع 129878743766 شماره پيگيري 743766_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>12:06:07</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 6037691636112419 متعلق به رضا رضائی از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1409556255 شماره پيگيري 217213_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>17:00:28</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از اينترنت 80080727 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت (2) - شماره مرجع 802845538622 شماره پيگيري 538622_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>21:50:48</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از اينترنت 80080727 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت (2) - شماره مرجع 802849163918 شماره پيگيري 163918_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>21:59:56</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از اينترنت 80080727 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت (2) - شماره مرجع 802849243876 شماره پيگيري 243876_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>22:39:23</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 50174468 - پذيرنده سوپر مارکت امیر حسین - پرداخت الکترونیک سامان - شماره مرجع 863285053737 شماره پيگيري 717193_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/26</t>
+  </si>
+  <si>
+    <t>15:58:03</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از اينترنت 10749015 - پذيرنده اسنپ - پرداخت الکترونیک سامان - شماره مرجع 224833459448 شماره پيگيري 951133_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>22:31:25</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 34068455 - پذيرنده Not - پرداخت الکترونیک سداد (2) - شماره مرجع 323711556075 شماره پيگيري 2968_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/27</t>
+  </si>
+  <si>
+    <t>10:57:09</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 894859 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت - شماره مرجع 352251325848 شماره پيگيري 325848_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>13:30:06</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از اينترنت 10749015 - پذيرنده اسنپ - پرداخت الکترونیک سامان - شماره مرجع 224836533053 شماره پيگيري 159738_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>17:32:02</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 4260744 - پذيرنده ساندویچی علیرضا - شرکت ایران کیش - شماره مرجع 000013792662 شماره پيگيري 127662_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>17:56:46</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 4260744 - پذيرنده ساندویچی علیرضا - شرکت ایران کیش - شماره مرجع 000013881278 شماره پيگيري 216278_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>19:55:07</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 31672699 - پذيرنده پایانه شماره 99627613 - پرداخت نوین آرین - شماره مرجع 517309636280 شماره پيگيري 475255_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>22:02:43</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 99080823 - پذيرنده ک بابی ب رادران س اکی - تجارت الکترونیک پارسیان - شماره مرجع 813385177088 شماره پيگيري 827307_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/28</t>
+  </si>
+  <si>
+    <t>06:46:56</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 98472140 - پذيرنده پرداخت الکترونیک سپهر - مبنا کارت آریا (اینفوتک) - شماره مرجع 129885542816 شماره پيگيري 542816_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>07:11:42</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 5142917 - پذيرنده TANAGHOLAT - آسان پرداخت پرشین - شماره مرجع 072258364019 شماره پيگيري 61056_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>07:27:09</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 5142917 - پذيرنده TANAGHOLAT - آسان پرداخت پرشین - شماره مرجع 072258514417 شماره پيگيري 61058_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/29</t>
+  </si>
+  <si>
+    <t>21:28:46</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 33178456 - پذيرنده Not - پرداخت الکترونیک سداد (2) - شماره مرجع 323740663467 شماره پيگيري 32361_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>21:35:03</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 20124059 - پذيرنده خرازی فاطیما - پرداخت نوین آرین - شماره مرجع 517345038494 شماره پيگيري 528718_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/30</t>
+  </si>
+  <si>
+    <t>09:33:06</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 15341545 - پذيرنده یکبار مصرف نگین - پرداخت الکترونیک سامان - شماره مرجع 863404682377 شماره پيگيري 630833_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>16:32:55</t>
+  </si>
+  <si>
+    <t>انتقال از کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) به کارت 6037691636112419 متعلق به رضا رضائی از اينترنت 115 - پذيرنده سايت اينترنتی - بانک قرض الحسنه رسالت - شماره مرجع 1423160836 شماره پيگيري 821942_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>1405/04/31</t>
+  </si>
+  <si>
+    <t>13:07:18</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 37207239 - پذيرنده Not - پرداخت الکترونیک سداد (2) - شماره مرجع 323756315730 شماره پيگيري 1399_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>کارمزد</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>12200</t>
+  </si>
+  <si>
+    <t>34600</t>
+  </si>
+  <si>
+    <t>1800</t>
+  </si>
+  <si>
+    <t>15400</t>
+  </si>
+  <si>
+    <t>21800</t>
+  </si>
+  <si>
+    <t>18600</t>
+  </si>
+  <si>
+    <t>پذیرایی آقای شفیعی و مشتری</t>
+  </si>
+  <si>
+    <t>رضایی حمل بار خرید</t>
+  </si>
+  <si>
+    <t>تیپاکس کلیشه پارت 44</t>
+  </si>
+  <si>
+    <t>هزینه ی ساخت کلیشه</t>
+  </si>
+  <si>
+    <t>خرید اینترنت شرکت</t>
+  </si>
+  <si>
+    <t>پلاستیک بسته بندی</t>
+  </si>
+  <si>
+    <t>نمایشگاه</t>
+  </si>
+  <si>
+    <t>حلوا مسقطی</t>
+  </si>
+  <si>
+    <t>قند</t>
+  </si>
+  <si>
+    <t>بیعانه ماشین حمل وسایل تا کرمانشاه</t>
+  </si>
+  <si>
+    <t>بلیت شیراز کرمانشاه</t>
+  </si>
+  <si>
+    <t>بلیت لار شیراز</t>
+  </si>
+  <si>
+    <t>بنزین</t>
+  </si>
+  <si>
+    <t>کت و شلوار</t>
+  </si>
+  <si>
+    <t>خیاطی</t>
+  </si>
+  <si>
+    <t>پیچ برای نصب تابلو در نمایشگاه</t>
+  </si>
+  <si>
+    <t>حمل بار خرید</t>
+  </si>
+  <si>
+    <t>اسنپ</t>
+  </si>
+  <si>
+    <t>تفتون و بتنور</t>
+  </si>
+  <si>
+    <t>خرید های حین سفر</t>
+  </si>
+  <si>
+    <t>قرص</t>
+  </si>
+  <si>
+    <t>شام</t>
+  </si>
+  <si>
+    <t>شب اول سکونت</t>
+  </si>
+  <si>
+    <t>پارت دوم هزینه ی حمل بار + 4 میلیون تومان که از حساب شخصیم زدم</t>
+  </si>
+  <si>
+    <t>بارنامه مخمل</t>
+  </si>
+  <si>
+    <t>66600</t>
+  </si>
+  <si>
+    <t>حمل خرید</t>
+  </si>
+  <si>
+    <t>روبان مشکی 3 عدد</t>
+  </si>
+  <si>
+    <t>روبان سرمه ای 25 عدد</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>129-134</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>پست جدلی</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>شارژ کارتریج پرینتر</t>
+  </si>
+  <si>
+    <t>211</t>
   </si>
 </sst>
 </file>
@@ -157,19 +888,17 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color theme="0"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Tahoma"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -230,6 +959,12 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -258,7 +993,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -277,7 +1012,7 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -292,12 +1027,6 @@
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -305,6 +1034,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -640,367 +1381,97 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="46" customWidth="1"/>
-    <col min="10" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-    </row>
-    <row r="2" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-    </row>
-    <row r="3" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="2">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="4">
-        <v>15400</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4">
-        <v>279812412</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="5">
-        <v>22600000</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
-        <v>257212412</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="4">
-        <v>400000</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
-        <v>256812412</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="5">
-        <v>6070000</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
-        <v>250742412</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="2">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="4">
-        <v>9193250</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
-        <v>241549162</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="5">
-        <v>9193250</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
-        <v>232355912</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A10:I10"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC7C2D1-AD44-4D29-A285-C2788A2DFD2C}">
-  <dimension ref="A1:P24"/>
-  <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:P95"/>
+  <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="78.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="76.5703125" customWidth="1"/>
+    <col min="6" max="8" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="8.140625" customWidth="1"/>
     <col min="13" max="15" width="10.5703125" customWidth="1"/>
-    <col min="16" max="16" width="45.28515625" customWidth="1"/>
+    <col min="16" max="16" width="52.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+    </row>
+    <row r="2" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-    </row>
-    <row r="2" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="9"/>
       <c r="B3" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>15</v>
       </c>
       <c r="F3" s="10">
         <v>22600000</v>
@@ -1020,23 +1491,23 @@
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
     </row>
-    <row r="4" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="14">
+        <v>15</v>
+      </c>
+      <c r="F4" s="12">
         <v>400000</v>
       </c>
       <c r="G4" s="4">
@@ -1045,38 +1516,38 @@
       <c r="H4" s="4">
         <v>256812412</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="11">
         <v>134</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
-      <c r="L4" s="13">
+      <c r="L4" s="11">
         <v>145</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
       <c r="P4" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="15">
+        <v>17</v>
+      </c>
+      <c r="F5" s="13">
         <v>6070000</v>
       </c>
       <c r="G5" s="5">
@@ -1085,38 +1556,38 @@
       <c r="H5" s="5">
         <v>250742412</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="11">
         <v>135</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
-      <c r="L5" s="13">
+      <c r="L5" s="11">
         <v>146</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
       <c r="P5" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="14">
+        <v>20</v>
+      </c>
+      <c r="F6" s="12">
         <v>9193250</v>
       </c>
       <c r="G6" s="4">
@@ -1125,38 +1596,38 @@
       <c r="H6" s="4">
         <v>241549162</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="11">
         <v>136</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
-      <c r="L6" s="13">
+      <c r="L6" s="11">
         <v>147</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
       <c r="P6" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="15">
+        <v>22</v>
+      </c>
+      <c r="F7" s="13">
         <v>9193250</v>
       </c>
       <c r="G7" s="5">
@@ -1165,42 +1636,4420 @@
       <c r="H7" s="5">
         <v>232355912</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="11">
         <v>136</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="13">
+      <c r="L7" s="11">
         <v>147</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="12">
+        <v>5285000</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>227070912</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P8" s="14" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="11" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="12" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="16" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="17" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="18" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="19" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="20" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="21" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="22" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="23" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="24" ht="22.5" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="D9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="13">
+        <v>9000</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>227061912</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O9" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="12">
+        <v>5000000</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>222061912</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O10" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P10" s="14" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="13">
+        <v>2758000</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>219303912</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="12">
+        <v>9000</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>219294912</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O12" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="13">
+        <v>9000000</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>210294912</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O13" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="12">
+        <v>1980000</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>208314912</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N14" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O14" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="13">
+        <v>3750000</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>204564912</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N15" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O15" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P15" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="12">
+        <v>7100000</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>197464912</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O16" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P16" s="15" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="13">
+        <v>28000000</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>169464912</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P17" s="15" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>167464912</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N18" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P18" s="14" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="13">
+        <v>15400</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5">
+        <v>167449512</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="P19" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="12">
+        <v>25800000</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <v>141649512</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N20" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O20" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P20" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="13">
+        <v>21800</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>141627712</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O21" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="P21" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="12">
+        <v>46980000</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>94647712</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N22" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O22" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P22" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="13">
+        <v>12200</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5">
+        <v>94635512</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O23" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="P23" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="12">
+        <v>13350000</v>
+      </c>
+      <c r="G24" s="4">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <v>81285512</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N24" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O24" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P24" s="15" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="13">
+        <v>59550</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5">
+        <v>81225962</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M25" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N25" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O25" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P25" s="15" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="12">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <v>51300000</v>
+      </c>
+      <c r="H26" s="4">
+        <v>132525962</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N26" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O26" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P26" s="14"/>
+    </row>
+    <row r="27" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="13">
+        <v>113000000</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5">
+        <v>19525962</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N27" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O27" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P27" s="15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="12">
+        <v>1500000</v>
+      </c>
+      <c r="G28" s="4">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4">
+        <v>18025962</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N28" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O28" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P28" s="15" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="13">
+        <v>220000</v>
+      </c>
+      <c r="G29" s="5">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5">
+        <v>17805962</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N29" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P29" s="15" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="12">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4">
+        <v>450000000</v>
+      </c>
+      <c r="H30" s="4">
+        <v>467805962</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="L30" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M30" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N30" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O30" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P30" s="14"/>
+    </row>
+    <row r="31" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="13">
+        <v>9000</v>
+      </c>
+      <c r="G31" s="5">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5">
+        <v>467796962</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N31" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O31" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="P31" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" s="12">
+        <v>4000000</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4">
+        <v>463796962</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="M32" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N32" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O32" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P32" s="14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="13">
+        <v>18600</v>
+      </c>
+      <c r="G33" s="5">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5">
+        <v>463778362</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N33" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O33" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="P33" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F34" s="12">
+        <v>39400000</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4">
+        <v>424378362</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="M34" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N34" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O34" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P34" s="14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="13">
+        <v>9000</v>
+      </c>
+      <c r="G35" s="5">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5">
+        <v>424369362</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N35" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O35" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="P35" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F36" s="12">
+        <v>1050000</v>
+      </c>
+      <c r="G36" s="4">
+        <v>0</v>
+      </c>
+      <c r="H36" s="4">
+        <v>423319362</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M36" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N36" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O36" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P36" s="15" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37" s="13">
+        <v>5150000</v>
+      </c>
+      <c r="G37" s="5">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5">
+        <v>418169362</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M37" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N37" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O37" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P37" s="15" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F38" s="12">
+        <v>2700000</v>
+      </c>
+      <c r="G38" s="4">
+        <v>0</v>
+      </c>
+      <c r="H38" s="4">
+        <v>415469362</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N38" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O38" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P38" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F39" s="13">
+        <v>150000</v>
+      </c>
+      <c r="G39" s="5">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5">
+        <v>415319362</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M39" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N39" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O39" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P39" s="15" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F40" s="12">
+        <v>11450000</v>
+      </c>
+      <c r="G40" s="4">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4">
+        <v>403869362</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M40" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N40" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O40" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P40" s="15" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F41" s="13">
+        <v>600000</v>
+      </c>
+      <c r="G41" s="5">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5">
+        <v>403269362</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M41" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N41" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O41" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P41" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F42" s="12">
+        <v>100000</v>
+      </c>
+      <c r="G42" s="4">
+        <v>0</v>
+      </c>
+      <c r="H42" s="4">
+        <v>403169362</v>
+      </c>
+      <c r="I42" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M42" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N42" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O42" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P42" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F43" s="13">
+        <v>1200000</v>
+      </c>
+      <c r="G43" s="5">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5">
+        <v>401969362</v>
+      </c>
+      <c r="I43" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M43" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N43" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O43" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P43" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" s="12">
+        <v>760000</v>
+      </c>
+      <c r="G44" s="4">
+        <v>0</v>
+      </c>
+      <c r="H44" s="4">
+        <v>401209362</v>
+      </c>
+      <c r="I44" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J44" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M44" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N44" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O44" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P44" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F45" s="13">
+        <v>1800</v>
+      </c>
+      <c r="G45" s="5">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5">
+        <v>401207562</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J45" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L45" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N45" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O45" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="P45" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F46" s="12">
+        <v>500000</v>
+      </c>
+      <c r="G46" s="4">
+        <v>0</v>
+      </c>
+      <c r="H46" s="4">
+        <v>400707562</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M46" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N46" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O46" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P46" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="13">
+        <v>15400</v>
+      </c>
+      <c r="G47" s="5">
+        <v>0</v>
+      </c>
+      <c r="H47" s="5">
+        <v>400692162</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L47" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N47" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O47" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="P47" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F48" s="12">
+        <v>25000000</v>
+      </c>
+      <c r="G48" s="4">
+        <v>0</v>
+      </c>
+      <c r="H48" s="4">
+        <v>375692162</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M48" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N48" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O48" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P48" s="15" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="13">
+        <v>9000</v>
+      </c>
+      <c r="G49" s="5">
+        <v>0</v>
+      </c>
+      <c r="H49" s="5">
+        <v>375683162</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J49" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L49" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N49" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O49" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="P49" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F50" s="12">
+        <v>200000</v>
+      </c>
+      <c r="G50" s="4">
+        <v>0</v>
+      </c>
+      <c r="H50" s="4">
+        <v>375483162</v>
+      </c>
+      <c r="I50" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J50" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M50" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N50" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O50" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P50" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="13">
+        <v>34600</v>
+      </c>
+      <c r="G51" s="5">
+        <v>0</v>
+      </c>
+      <c r="H51" s="5">
+        <v>375448562</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J51" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L51" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N51" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O51" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="P51" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F52" s="12">
+        <v>90000000</v>
+      </c>
+      <c r="G52" s="4">
+        <v>0</v>
+      </c>
+      <c r="H52" s="4">
+        <v>285448562</v>
+      </c>
+      <c r="I52" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J52" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M52" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N52" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O52" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P52" s="15" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F53" s="13">
+        <v>1900000</v>
+      </c>
+      <c r="G53" s="5">
+        <v>0</v>
+      </c>
+      <c r="H53" s="5">
+        <v>283548562</v>
+      </c>
+      <c r="I53" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J53" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M53" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N53" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O53" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P53" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F54" s="12">
+        <v>1150000</v>
+      </c>
+      <c r="G54" s="4">
+        <v>0</v>
+      </c>
+      <c r="H54" s="4">
+        <v>282398562</v>
+      </c>
+      <c r="I54" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J54" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M54" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N54" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O54" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P54" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F55" s="13">
+        <v>14000000</v>
+      </c>
+      <c r="G55" s="5">
+        <v>0</v>
+      </c>
+      <c r="H55" s="5">
+        <v>268398562</v>
+      </c>
+      <c r="I55" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J55" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K55" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M55" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N55" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O55" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P55" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F56" s="12">
+        <v>1800000</v>
+      </c>
+      <c r="G56" s="4">
+        <v>0</v>
+      </c>
+      <c r="H56" s="4">
+        <v>266598562</v>
+      </c>
+      <c r="I56" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J56" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M56" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N56" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O56" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P56" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F57" s="13">
+        <v>1150000</v>
+      </c>
+      <c r="G57" s="5">
+        <v>0</v>
+      </c>
+      <c r="H57" s="5">
+        <v>265448562</v>
+      </c>
+      <c r="I57" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J57" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M57" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N57" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O57" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P57" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F58" s="12">
+        <v>1050000</v>
+      </c>
+      <c r="G58" s="4">
+        <v>0</v>
+      </c>
+      <c r="H58" s="4">
+        <v>264398562</v>
+      </c>
+      <c r="I58" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J58" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M58" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N58" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O58" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P58" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F59" s="13">
+        <v>500000</v>
+      </c>
+      <c r="G59" s="5">
+        <v>0</v>
+      </c>
+      <c r="H59" s="5">
+        <v>263898562</v>
+      </c>
+      <c r="I59" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J59" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K59" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M59" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N59" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O59" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P59" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F60" s="12">
+        <v>830000</v>
+      </c>
+      <c r="G60" s="4">
+        <v>0</v>
+      </c>
+      <c r="H60" s="4">
+        <v>263068562</v>
+      </c>
+      <c r="I60" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J60" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K60" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M60" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N60" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O60" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P60" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F61" s="13">
+        <v>1250000</v>
+      </c>
+      <c r="G61" s="5">
+        <v>0</v>
+      </c>
+      <c r="H61" s="5">
+        <v>261818562</v>
+      </c>
+      <c r="I61" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J61" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K61" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M61" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N61" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O61" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P61" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F62" s="12">
+        <v>920000</v>
+      </c>
+      <c r="G62" s="4">
+        <v>0</v>
+      </c>
+      <c r="H62" s="4">
+        <v>260898562</v>
+      </c>
+      <c r="I62" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J62" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K62" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M62" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N62" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O62" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P62" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F63" s="13">
+        <v>270000</v>
+      </c>
+      <c r="G63" s="5">
+        <v>0</v>
+      </c>
+      <c r="H63" s="5">
+        <v>260628562</v>
+      </c>
+      <c r="I63" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J63" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M63" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N63" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O63" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P63" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F64" s="12">
+        <v>600000</v>
+      </c>
+      <c r="G64" s="4">
+        <v>0</v>
+      </c>
+      <c r="H64" s="4">
+        <v>260028562</v>
+      </c>
+      <c r="I64" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J64" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K64" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M64" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N64" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O64" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P64" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F65" s="13">
+        <v>700000</v>
+      </c>
+      <c r="G65" s="5">
+        <v>0</v>
+      </c>
+      <c r="H65" s="5">
+        <v>259328562</v>
+      </c>
+      <c r="I65" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J65" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K65" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M65" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N65" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O65" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P65" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F66" s="12">
+        <v>66600</v>
+      </c>
+      <c r="G66" s="4">
+        <v>0</v>
+      </c>
+      <c r="H66" s="4">
+        <v>259261962</v>
+      </c>
+      <c r="I66" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J66" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K66" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L66" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N66" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O66" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="P66" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="13">
+        <v>12200</v>
+      </c>
+      <c r="G67" s="5">
+        <v>0</v>
+      </c>
+      <c r="H67" s="5">
+        <v>259249762</v>
+      </c>
+      <c r="I67" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J67" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K67" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L67" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N67" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O67" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="P67" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F68" s="12">
+        <v>16300000</v>
+      </c>
+      <c r="G68" s="4">
+        <v>0</v>
+      </c>
+      <c r="H68" s="4">
+        <v>242949762</v>
+      </c>
+      <c r="I68" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="J68" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K68" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="M68" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N68" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O68" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P68" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F69" s="13">
+        <v>1280000</v>
+      </c>
+      <c r="G69" s="5">
+        <v>0</v>
+      </c>
+      <c r="H69" s="5">
+        <v>241669762</v>
+      </c>
+      <c r="I69" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J69" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K69" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M69" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N69" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O69" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P69" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F70" s="12">
+        <v>600000</v>
+      </c>
+      <c r="G70" s="4">
+        <v>0</v>
+      </c>
+      <c r="H70" s="4">
+        <v>241069762</v>
+      </c>
+      <c r="I70" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J70" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K70" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M70" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N70" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O70" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P70" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F71" s="13">
+        <v>119000</v>
+      </c>
+      <c r="G71" s="5">
+        <v>0</v>
+      </c>
+      <c r="H71" s="5">
+        <v>240950762</v>
+      </c>
+      <c r="I71" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J71" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K71" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M71" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N71" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O71" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P71" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F72" s="12">
+        <v>46980000</v>
+      </c>
+      <c r="G72" s="4">
+        <v>0</v>
+      </c>
+      <c r="H72" s="4">
+        <v>193970762</v>
+      </c>
+      <c r="I72" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J72" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M72" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N72" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O72" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P72" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="13">
+        <v>9000</v>
+      </c>
+      <c r="G73" s="5">
+        <v>0</v>
+      </c>
+      <c r="H73" s="5">
+        <v>193961762</v>
+      </c>
+      <c r="I73" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J73" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K73" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L73" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N73" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O73" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="P73" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F74" s="12">
+        <v>4000000</v>
+      </c>
+      <c r="G74" s="4">
+        <v>0</v>
+      </c>
+      <c r="H74" s="4">
+        <v>189961762</v>
+      </c>
+      <c r="I74" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="J74" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="M74" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N74" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O74" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P74" s="14" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F75" s="13">
+        <v>1090000</v>
+      </c>
+      <c r="G75" s="5">
+        <v>0</v>
+      </c>
+      <c r="H75" s="5">
+        <v>188871762</v>
+      </c>
+      <c r="I75" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J75" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K75" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M75" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N75" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O75" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P75" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F76" s="12">
+        <v>60000</v>
+      </c>
+      <c r="G76" s="4">
+        <v>0</v>
+      </c>
+      <c r="H76" s="4">
+        <v>188811762</v>
+      </c>
+      <c r="I76" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J76" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K76" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M76" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N76" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O76" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P76" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F77" s="13">
+        <v>1090000</v>
+      </c>
+      <c r="G77" s="5">
+        <v>0</v>
+      </c>
+      <c r="H77" s="5">
+        <v>187721762</v>
+      </c>
+      <c r="I77" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J77" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K77" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M77" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N77" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O77" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P77" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F78" s="12">
+        <v>50000</v>
+      </c>
+      <c r="G78" s="4">
+        <v>0</v>
+      </c>
+      <c r="H78" s="4">
+        <v>187671762</v>
+      </c>
+      <c r="I78" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J78" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K78" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M78" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N78" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O78" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P78" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F79" s="13">
+        <v>1220000</v>
+      </c>
+      <c r="G79" s="5">
+        <v>0</v>
+      </c>
+      <c r="H79" s="5">
+        <v>186451762</v>
+      </c>
+      <c r="I79" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J79" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K79" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M79" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N79" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O79" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P79" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F80" s="12">
+        <v>400000</v>
+      </c>
+      <c r="G80" s="4">
+        <v>0</v>
+      </c>
+      <c r="H80" s="4">
+        <v>186051762</v>
+      </c>
+      <c r="I80" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J80" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K80" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L80" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M80" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N80" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O80" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P80" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F81" s="13">
+        <v>2500000</v>
+      </c>
+      <c r="G81" s="5">
+        <v>0</v>
+      </c>
+      <c r="H81" s="5">
+        <v>183551762</v>
+      </c>
+      <c r="I81" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J81" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K81" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M81" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N81" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O81" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P81" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F82" s="12">
+        <v>1070000</v>
+      </c>
+      <c r="G82" s="4">
+        <v>0</v>
+      </c>
+      <c r="H82" s="4">
+        <v>182481762</v>
+      </c>
+      <c r="I82" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J82" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K82" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L82" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M82" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N82" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O82" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P82" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F83" s="13">
+        <v>2450000</v>
+      </c>
+      <c r="G83" s="5">
+        <v>0</v>
+      </c>
+      <c r="H83" s="5">
+        <v>180031762</v>
+      </c>
+      <c r="I83" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J83" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K83" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L83" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M83" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N83" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O83" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P83" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F84" s="12">
+        <v>350000</v>
+      </c>
+      <c r="G84" s="4">
+        <v>0</v>
+      </c>
+      <c r="H84" s="4">
+        <v>179681762</v>
+      </c>
+      <c r="I84" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J84" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K84" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L84" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M84" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N84" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O84" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P84" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F85" s="13">
+        <v>350000</v>
+      </c>
+      <c r="G85" s="5">
+        <v>0</v>
+      </c>
+      <c r="H85" s="5">
+        <v>179331762</v>
+      </c>
+      <c r="I85" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J85" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K85" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L85" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M85" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N85" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O85" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P85" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F86" s="12">
+        <v>11700000</v>
+      </c>
+      <c r="G86" s="4">
+        <v>0</v>
+      </c>
+      <c r="H86" s="4">
+        <v>167631762</v>
+      </c>
+      <c r="I86" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J86" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K86" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L86" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M86" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N86" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O86" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P86" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F87" s="13">
+        <v>14720000</v>
+      </c>
+      <c r="G87" s="5">
+        <v>0</v>
+      </c>
+      <c r="H87" s="5">
+        <v>152911762</v>
+      </c>
+      <c r="I87" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J87" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K87" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L87" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M87" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N87" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O87" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P87" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F88" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="G88" s="4">
+        <v>0</v>
+      </c>
+      <c r="H88" s="4">
+        <v>151911762</v>
+      </c>
+      <c r="I88" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J88" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K88" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L88" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M88" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N88" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O88" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P88" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F89" s="13">
+        <v>1500000</v>
+      </c>
+      <c r="G89" s="5">
+        <v>0</v>
+      </c>
+      <c r="H89" s="5">
+        <v>150411762</v>
+      </c>
+      <c r="I89" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J89" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K89" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L89" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M89" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N89" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O89" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P89" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F90" s="12">
+        <v>1950000</v>
+      </c>
+      <c r="G90" s="4">
+        <v>0</v>
+      </c>
+      <c r="H90" s="4">
+        <v>148461762</v>
+      </c>
+      <c r="I90" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="J90" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K90" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L90" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="M90" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N90" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O90" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P90" s="14" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F91" s="13">
+        <v>16000000</v>
+      </c>
+      <c r="G91" s="5">
+        <v>0</v>
+      </c>
+      <c r="H91" s="5">
+        <v>132461762</v>
+      </c>
+      <c r="I91" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="J91" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K91" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L91" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="M91" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N91" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O91" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P91" s="14" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F92" s="12">
+        <v>20340000</v>
+      </c>
+      <c r="G92" s="4">
+        <v>0</v>
+      </c>
+      <c r="H92" s="4">
+        <v>112121762</v>
+      </c>
+      <c r="I92" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="J92" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K92" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L92" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="M92" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N92" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O92" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P92" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F93" s="13">
+        <v>9000</v>
+      </c>
+      <c r="G93" s="5">
+        <v>0</v>
+      </c>
+      <c r="H93" s="5">
+        <v>112112762</v>
+      </c>
+      <c r="I93" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J93" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K93" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L93" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M93" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="N93" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O93" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="P93" s="14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F94" s="12">
+        <v>4000000</v>
+      </c>
+      <c r="G94" s="4">
+        <v>0</v>
+      </c>
+      <c r="H94" s="4">
+        <v>108112762</v>
+      </c>
+      <c r="I94" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="J94" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K94" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L94" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="M94" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N94" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O94" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P94" s="14" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F95" s="13">
+        <v>5500000</v>
+      </c>
+      <c r="G95" s="5">
+        <v>0</v>
+      </c>
+      <c r="H95" s="5">
+        <v>102612762</v>
+      </c>
+      <c r="I95" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="J95" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K95" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L95" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="M95" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="N95" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O95" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="P95" s="14" t="s">
+        <v>280</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A2:P95" xr:uid="{1BC7C2D1-AD44-4D29-A285-C2788A2DFD2C}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/حسابداری/بانک ها/رسالت ابوالفضل/1405/14050331 - 14050431.xlsx
+++ b/حسابداری/بانک ها/رسالت ابوالفضل/1405/14050331 - 14050431.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\رسالت ابوالفضل\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34F217B-EDF1-4E10-B694-19A458E69239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDFAB1E-B629-4C22-9F62-DAD7A01BED37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6044,7 +6044,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P95" xr:uid="{1BC7C2D1-AD44-4D29-A285-C2788A2DFD2C}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
